--- a/Partial-Entries-Converted-to-Apps/06-29-26-flagship-partials-converted-to-apps-this-week.xlsx
+++ b/Partial-Entries-Converted-to-Apps/06-29-26-flagship-partials-converted-to-apps-this-week.xlsx
@@ -415,13 +415,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20.9" customWidth="1" min="1" max="1"/>
     <col width="19.8" customWidth="1" min="2" max="2"/>
     <col width="14.3" customWidth="1" min="3" max="3"/>
-    <col width="34.1" customWidth="1" min="4" max="4"/>
+    <col width="41.8" customWidth="1" min="4" max="4"/>
     <col width="33" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -455,270 +455,486 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>003QP00001b1PRZ</t>
+          <t>003QP00000mjjjn</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Yetunde</t>
+          <t>Leonard</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>Olori</t>
+          <t>Gashugi</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>toluolori@gmail.com</t>
+          <t>gashugil@yahoo.com</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>06-15-2026</t>
+          <t>06-22-2026</t>
         </is>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>003QP00001b8dw2</t>
+          <t>003QP00001c09l0</t>
         </is>
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>Erastus</t>
+          <t>Edgar</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>Odhiambo</t>
+          <t>Phiri</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>info@dynamicsera.com</t>
+          <t>edgarphiri23@gmail.com</t>
         </is>
       </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
-          <t>06-15-2026</t>
+          <t>06-22-2026</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>003QP00001b89Zp</t>
+          <t>003QP00001cG4CY</t>
         </is>
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>Vinod Kumar</t>
+          <t>Hanaa</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>Verma</t>
+          <t>LAHNITI</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>vinodverma150791@gmail.com</t>
+          <t>lahnitihanaa@gmail.com</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>06-15-2026</t>
+          <t>06-23-2026</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>003QP00001b5xCv</t>
+          <t>003QP00001cDDnU</t>
         </is>
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>Fyness</t>
+          <t>Efaz</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>Kayaye</t>
+          <t>Tahmid</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>fynesskayaye@gmail.com</t>
+          <t>efaztahmid057@gmail.com</t>
         </is>
       </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
-          <t>06-15-2026</t>
+          <t>06-23-2026</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>003QP00001b56yJ</t>
+          <t>003QP00001c8FMr</t>
         </is>
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>Oarabile</t>
+          <t>ABATI</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>Baisi</t>
+          <t>Faith</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>rabiebaisi@gmail.com</t>
+          <t>oluwafowokemi2001@gmail.com</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr">
         <is>
-          <t>06-15-2026</t>
+          <t>06-23-2026</t>
         </is>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>003QP00001b8oUs</t>
+          <t>003QP00001cDxK1</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>Shafin</t>
+          <t>Virat Kumar</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>Tank</t>
+          <t>Sen</t>
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>shafintank@gmail.com</t>
+          <t>kumarvirat053@gmail.com</t>
         </is>
       </c>
       <c r="E7" s="1" t="inlineStr">
         <is>
-          <t>06-15-2026</t>
+          <t>06-23-2026</t>
         </is>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>003QP00001YOzay</t>
+          <t>003QP00001cM5x8</t>
         </is>
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>Aplonia siwayi</t>
+          <t>VICTOR</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>Antunes</t>
+          <t>USOH</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>antunesaplomia@gmail.com</t>
+          <t>usohvictor179@gmail.com</t>
         </is>
       </c>
       <c r="E8" s="1" t="inlineStr">
         <is>
-          <t>06-16-2026</t>
+          <t>06-24-2026</t>
         </is>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>003QP00001baLjF</t>
+          <t>003QP00001cR4h5</t>
         </is>
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>Alexa</t>
+          <t>Ganesh</t>
         </is>
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>Diaz</t>
+          <t>Paudel</t>
         </is>
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>alexa@bebettertogether.org</t>
+          <t>ganeshpaudelparbat@gmail.com</t>
         </is>
       </c>
       <c r="E9" s="1" t="inlineStr">
         <is>
-          <t>06-18-2026</t>
+          <t>06-24-2026</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>003QP00001bnnjK</t>
+          <t>003QP00001cN8wE</t>
         </is>
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>KEVIN</t>
+          <t>Geiczar Ross</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>ATIMANGO</t>
+          <t>Real</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>kevin@elevatehealth.org</t>
+          <t>gdreal2024@gmail.com</t>
         </is>
       </c>
       <c r="E10" s="1" t="inlineStr">
         <is>
-          <t>06-19-2026</t>
+          <t>06-24-2026</t>
         </is>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>003QP000017Lvd7</t>
+          <t>003QP00001Yg0nc</t>
         </is>
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>Dr Tori</t>
+          <t>Ugonna</t>
         </is>
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>Brown</t>
+          <t>Achebe</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
-          <t>freshcommunityinc@gmail.com</t>
+          <t>ugonnaachebe@gmail.com</t>
         </is>
       </c>
       <c r="E11" s="1" t="inlineStr">
         <is>
-          <t>06-19-2026</t>
+          <t>06-25-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>003QP00001cXRfo</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>CHANDRIKA RAY</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>sooklall</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="inlineStr">
+        <is>
+          <t>kreshansooklall@gmail.com</t>
+        </is>
+      </c>
+      <c r="E12" s="1" t="inlineStr">
+        <is>
+          <t>06-25-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>003QP00001cSSj0</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>Wangiwe Joanna</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>Kambuzi</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="inlineStr">
+        <is>
+          <t>wangiwe@emergelivelihoods.org</t>
+        </is>
+      </c>
+      <c r="E13" s="1" t="inlineStr">
+        <is>
+          <t>06-25-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>003QP00001cdHDx</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>Immaculate</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>Wesonga</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="inlineStr">
+        <is>
+          <t>undugu.empowerment101@gmail.com</t>
+        </is>
+      </c>
+      <c r="E14" s="1" t="inlineStr">
+        <is>
+          <t>06-26-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>003QP00001cbBrW</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>Joyce</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="inlineStr">
+        <is>
+          <t>Rugano</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="inlineStr">
+        <is>
+          <t>admin@ecorich.co.ke</t>
+        </is>
+      </c>
+      <c r="E15" s="1" t="inlineStr">
+        <is>
+          <t>06-26-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>003QP00001cmowz</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>Nandom</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="inlineStr">
+        <is>
+          <t>Mampak</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="inlineStr">
+        <is>
+          <t>pakflame@gmail.com</t>
+        </is>
+      </c>
+      <c r="E16" s="1" t="inlineStr">
+        <is>
+          <t>06-27-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>003QP00000mkVwQ</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>Austinline</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>Ekweogu</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="inlineStr">
+        <is>
+          <t>austinlinechizobaekweogu@gmail.com</t>
+        </is>
+      </c>
+      <c r="E17" s="1" t="inlineStr">
+        <is>
+          <t>06-27-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>0033h00001HQshj</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>Blaise Tanam</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="inlineStr">
+        <is>
+          <t>Fonguh</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="inlineStr">
+        <is>
+          <t>blaisefonguh99@gmail.com</t>
+        </is>
+      </c>
+      <c r="E18" s="1" t="inlineStr">
+        <is>
+          <t>06-28-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>003QP00000UEZkb</t>
+        </is>
+      </c>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>Ilgar</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t>Taghiyev</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="inlineStr">
+        <is>
+          <t>info@atruck.me</t>
+        </is>
+      </c>
+      <c r="E19" s="1" t="inlineStr">
+        <is>
+          <t>06-29-2026</t>
         </is>
       </c>
     </row>
